--- a/out/thesis/tables/create_vs_announcement_paired_comparison.xlsx
+++ b/out/thesis/tables/create_vs_announcement_paired_comparison.xlsx
@@ -643,34 +643,34 @@
         <v>124</v>
       </c>
       <c r="E5">
-        <v>0.01093878993625925</v>
+        <v>0.0113319590387578</v>
       </c>
       <c r="F5">
         <v>0.01463933346462561</v>
       </c>
       <c r="G5">
-        <v>0.003700543528366357</v>
+        <v>0.003307374425867811</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.001759490899643615</v>
+        <v>0.001778316453652553</v>
       </c>
       <c r="J5">
         <v>0.1774193548387097</v>
       </c>
       <c r="K5">
-        <v>0.1451612903225807</v>
+        <v>0.1532258064516129</v>
       </c>
       <c r="L5">
-        <v>0.8159668185945017</v>
+        <v>0.7317352667006797</v>
       </c>
       <c r="M5">
-        <v>0.4160964929407555</v>
+        <v>0.4657220309231935</v>
       </c>
       <c r="N5">
-        <v>0.3540922833290097</v>
+        <v>0.4202122508122557</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -684,7 +684,34 @@
         <v>32</v>
       </c>
       <c r="D6">
+        <v>21</v>
+      </c>
+      <c r="E6">
+        <v>-0.01169630487040147</v>
+      </c>
+      <c r="F6">
+        <v>-0.01313648395624121</v>
+      </c>
+      <c r="G6">
+        <v>-0.001440179085839739</v>
+      </c>
+      <c r="H6">
         <v>0</v>
+      </c>
+      <c r="I6">
+        <v>-0.002855124911595137</v>
+      </c>
+      <c r="J6">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="K6">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="L6">
+        <v>-0.3456148124597409</v>
+      </c>
+      <c r="M6">
+        <v>0.733241005985824</v>
       </c>
     </row>
     <row r="7" spans="1:14">
